--- a/LECTURER AND STAFF.xlsx
+++ b/LECTURER AND STAFF.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAZER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAZER\Desktop\Rockson project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83E8BC5D-B8B2-49E8-BFE6-B44B9083A8D1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BCBEDA-746F-4B9E-9CD1-2628D8DFA408}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" xr2:uid="{DFF878A8-1D9E-4282-804F-61D90245E433}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>ROCKSON DJAGO</t>
   </si>
@@ -454,49 +454,37 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A4" s="1"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
